--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="518">
   <si>
     <t>ID</t>
   </si>
@@ -582,90 +582,93 @@
     <t>在楼下的办公室里，你的朋友们已经问过这个问题了。</t>
   </si>
   <si>
+    <t>parallel(charfadeout(L,1);charfadein(R,1))</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Sophia; 层级=50</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>她头也不回地继续检查这间电刑椅的每一处缝隙，指尖沾到的血沫顺着椅腿滴落到冰冷的瓷砖上，在惨白灯光下晕开一小片不规则的暗褐色痕迹。</t>
+  </si>
+  <si>
+    <t>charfadeout(R,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=51</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>她定睛一瞧，脸上的表情瞬间变得凝重。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=52</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>这是一句话。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Sophia; 层级=53</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>克拉克挤进去半个身子，手电光束顺着她指尖的方向照去，果然在椅腿和地面接触的内侧，刻着一行由刚刚淌下的血渍拓出的一行小字。</t>
+  </si>
+  <si>
+    <t>charfadeout(L,1)&amp;bgfade(sntzm_final(3)_104,1)</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=54</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>Clark_default</t>
+  </si>
+  <si>
+    <t>终点亦是起点，烈火即为笼网的终局。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Clark; 层级=55</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>克拉克皱着眉把这句话念出来，后半句的笔迹远比前半句潦草，像是亚波伦耗尽最后一丝力气才刻完。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_pb; 层级=56</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>这是典型的控梦效应，他一定还在周围的某处。</t>
+  </si>
+  <si>
+    <t>源类型=type:txt_Sophia; 层级=57</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>这个混账东西，到死都要留这么一句没头没尾的谜语。</t>
+  </si>
+  <si>
     <t>parallel(charfadeout(L,1)&amp;charfadein(R,1))</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=50</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>她头也不回地继续检查这间电刑椅的每一处缝隙，指尖沾到的血沫顺着椅腿滴落到冰冷的瓷砖上，在惨白灯光下晕开一小片不规则的暗褐色痕迹。</t>
-  </si>
-  <si>
-    <t>charfadeout(R,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=51</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>她定睛一瞧，脸上的表情瞬间变得凝重。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=52</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>这是一句话。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Sophia; 层级=53</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>克拉克挤进去半个身子，手电光束顺着她指尖的方向照去，果然在椅腿和地面接触的内侧，刻着一行由刚刚淌下的血渍拓出的一行小字。</t>
-  </si>
-  <si>
-    <t>charfadeout(L,1)&amp;bgfade(sntzm_final(3)_104,1)</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=54</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>Clark_default</t>
-  </si>
-  <si>
-    <t>终点亦是起点，烈火即为笼网的终局。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Clark; 层级=55</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
-    <t>克拉克皱着眉把这句话念出来，后半句的笔迹远比前半句潦草，像是亚波伦耗尽最后一丝力气才刻完。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=56</t>
-  </si>
-  <si>
-    <t>107</t>
-  </si>
-  <si>
-    <t>这是典型的控梦效应，他一定还在周围的某处。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_Sophia; 层级=57</t>
-  </si>
-  <si>
-    <t>108</t>
-  </si>
-  <si>
-    <t>这个混账东西，到死都要留这么一句没头没尾的谜语。</t>
-  </si>
-  <si>
     <t>源类型=type:txt_David; 层级=58</t>
   </si>
   <si>
@@ -715,6 +718,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1002,7 +1010,7 @@
     <t>话音未落，一阵金属与肉体的沉闷碰撞应声响起，来源正是那扇你们进来时随手带上的，现在正被那个在摄像头里看到的怪物用力顶撞的门，仿佛一种刻意的示威——用切实的力量嘲讽着克拉克不堪一用的正义感。</t>
   </si>
   <si>
-    <t>charfadeout(L,1)&amp;bgfade(sntzm_david4F(4)_19,1)&amp;shake(screen,0.5,10)</t>
+    <t>charfadeout(L,1)&amp;bgfade(sntzm_david4F(4)_19,1)&amp;parallel(shake(screen,0.5,10);playsfx(MetallicThud))</t>
   </si>
   <si>
     <t>19</t>
@@ -1069,6 +1077,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -5106,15 +5119,15 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="L60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" ht="27" spans="1:12">
       <c r="A61" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -5132,7 +5145,7 @@
         <v>131</v>
       </c>
       <c r="G61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5147,12 +5160,12 @@
         <v>186</v>
       </c>
       <c r="L61" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" ht="40.5" spans="1:12">
       <c r="A62" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5170,7 +5183,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5182,15 +5195,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B63" t="s">
         <v>158</v>
@@ -5208,7 +5221,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5223,12 +5236,12 @@
         <v>15</v>
       </c>
       <c r="L63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B64" t="s">
         <v>50</v>
@@ -5246,7 +5259,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5261,12 +5274,12 @@
         <v>15</v>
       </c>
       <c r="L64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" ht="30" spans="1:12">
       <c r="A65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B65" t="s">
         <v>121</v>
@@ -5284,7 +5297,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5296,15 +5309,15 @@
         <v>15</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L65" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" ht="54" spans="1:12">
       <c r="A66" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B66" t="s">
         <v>50</v>
@@ -5322,7 +5335,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5337,12 +5350,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B67" t="s">
         <v>22</v>
@@ -5360,7 +5373,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5380,7 +5393,7 @@
     </row>
     <row r="68" ht="30" spans="1:12">
       <c r="A68" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5398,7 +5411,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5413,12 +5426,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="69" ht="55.5" spans="1:12">
       <c r="A69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
@@ -5436,7 +5449,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5451,12 +5464,12 @@
         <v>15</v>
       </c>
       <c r="L69" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B70" t="s">
         <v>22</v>
@@ -5474,7 +5487,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5489,12 +5502,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="71" ht="54" spans="1:12">
       <c r="A71" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B71" t="s">
         <v>22</v>
@@ -5512,7 +5525,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5527,12 +5540,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="72" ht="42" spans="1:12">
       <c r="A72" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B72" t="s">
         <v>13</v>
@@ -5550,7 +5563,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5570,7 +5583,7 @@
     </row>
     <row r="73" ht="67.5" spans="1:12">
       <c r="A73" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
@@ -5588,7 +5601,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5603,12 +5616,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="74" ht="30" spans="1:12">
       <c r="A74" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B74" t="s">
         <v>50</v>
@@ -5626,7 +5639,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5641,12 +5654,12 @@
         <v>37</v>
       </c>
       <c r="L74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="75" ht="67.5" spans="1:12">
       <c r="A75" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5664,7 +5677,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5679,12 +5692,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B76" t="s">
         <v>22</v>
@@ -5702,7 +5715,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5722,7 +5735,7 @@
     </row>
     <row r="77" ht="42" spans="1:12">
       <c r="A77" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
         <v>22</v>
@@ -5740,7 +5753,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5755,12 +5768,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="78" ht="30" spans="1:12">
       <c r="A78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5778,7 +5791,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5793,12 +5806,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="79" ht="69" spans="1:12">
       <c r="A79" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B79" t="s">
         <v>22</v>
@@ -5816,7 +5829,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5836,7 +5849,7 @@
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B80" t="s">
         <v>50</v>
@@ -5854,7 +5867,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5869,12 +5882,12 @@
         <v>37</v>
       </c>
       <c r="L80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="81" ht="30" spans="1:12">
       <c r="A81" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B81" t="s">
         <v>22</v>
@@ -5892,7 +5905,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5912,7 +5925,7 @@
     </row>
     <row r="82" ht="40.5" spans="1:12">
       <c r="A82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5930,7 +5943,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5950,7 +5963,7 @@
     </row>
     <row r="83" ht="42" spans="1:12">
       <c r="A83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B83" t="s">
         <v>22</v>
@@ -5968,7 +5981,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5980,12 +5993,12 @@
         <v>15</v>
       </c>
       <c r="L83" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6003,7 +6016,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6023,7 +6036,7 @@
     </row>
     <row r="85" ht="42" spans="1:12">
       <c r="A85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B85" t="s">
         <v>22</v>
@@ -6041,7 +6054,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6056,12 +6069,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="86" ht="30" spans="1:12">
       <c r="A86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B86" t="s">
         <v>50</v>
@@ -6079,7 +6092,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6094,12 +6107,12 @@
         <v>37</v>
       </c>
       <c r="L86" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B87" t="s">
         <v>22</v>
@@ -6117,7 +6130,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6132,12 +6145,12 @@
         <v>146</v>
       </c>
       <c r="L87" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B88" t="s">
         <v>22</v>
@@ -6155,7 +6168,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6170,12 +6183,12 @@
         <v>15</v>
       </c>
       <c r="L88" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="89" ht="30" spans="1:12">
       <c r="A89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6193,7 +6206,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6213,7 +6226,7 @@
     </row>
     <row r="90" ht="40.5" spans="1:12">
       <c r="A90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
@@ -6231,7 +6244,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6246,12 +6259,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="91" ht="30" spans="1:12">
       <c r="A91" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B91" t="s">
         <v>22</v>
@@ -6269,7 +6282,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6284,12 +6297,12 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="92" ht="55.5" spans="1:12">
       <c r="A92" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6307,7 +6320,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6327,7 +6340,7 @@
     </row>
     <row r="93" ht="67.5" spans="1:12">
       <c r="A93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B93" t="s">
         <v>13</v>
@@ -6342,7 +6355,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6357,12 +6370,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="94" ht="54" spans="1:12">
       <c r="A94" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B94" t="s">
         <v>22</v>
@@ -6380,7 +6393,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6395,12 +6408,12 @@
         <v>146</v>
       </c>
       <c r="L94" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="95" ht="54" spans="1:12">
       <c r="A95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B95" t="s">
         <v>93</v>
@@ -6418,7 +6431,7 @@
         <v>199</v>
       </c>
       <c r="G95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6430,15 +6443,15 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>182</v>
+        <v>210</v>
       </c>
       <c r="L95" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="96" ht="40.5" spans="1:12">
       <c r="A96" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6456,7 +6469,7 @@
         <v>199</v>
       </c>
       <c r="G96" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6476,7 +6489,7 @@
     </row>
     <row r="97" ht="42" spans="1:12">
       <c r="A97" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B97" t="s">
         <v>22</v>
@@ -6494,7 +6507,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6509,12 +6522,12 @@
         <v>146</v>
       </c>
       <c r="L97" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="98" ht="69" spans="1:12">
       <c r="A98" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6532,7 +6545,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6544,7 +6557,7 @@
         <v>15</v>
       </c>
       <c r="K98" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="L98" t="s">
         <v>126</v>
@@ -6552,7 +6565,7 @@
     </row>
     <row r="99" ht="40.5" spans="1:12">
       <c r="A99" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
@@ -6570,7 +6583,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6585,12 +6598,12 @@
         <v>146</v>
       </c>
       <c r="L99" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="100" ht="30" spans="1:12">
       <c r="A100" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B100" t="s">
         <v>22</v>
@@ -6608,7 +6621,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6620,12 +6633,12 @@
         <v>15</v>
       </c>
       <c r="L100" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="101" ht="40.5" spans="1:12">
       <c r="A101" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B101" t="s">
         <v>13</v>
@@ -6643,7 +6656,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6663,7 +6676,7 @@
     </row>
     <row r="102" ht="43.5" spans="1:12">
       <c r="A102" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
@@ -6681,7 +6694,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6696,12 +6709,12 @@
         <v>15</v>
       </c>
       <c r="L102" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="103" ht="54" spans="1:12">
       <c r="A103" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
@@ -6719,7 +6732,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6734,12 +6747,12 @@
         <v>15</v>
       </c>
       <c r="L103" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="104" ht="30" spans="1:12">
       <c r="A104" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B104" t="s">
         <v>22</v>
@@ -6757,7 +6770,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
@@ -6772,12 +6785,12 @@
         <v>15</v>
       </c>
       <c r="L104" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="105" ht="55.5" spans="1:12">
       <c r="A105" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B105" t="s">
         <v>13</v>
@@ -6795,7 +6808,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
@@ -6815,7 +6828,7 @@
     </row>
     <row r="106" ht="40.5" spans="1:12">
       <c r="A106" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B106" t="s">
         <v>13</v>
@@ -6833,7 +6846,7 @@
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H106" t="s">
         <v>15</v>
@@ -6845,10 +6858,10 @@
         <v>15</v>
       </c>
       <c r="K106" s="3" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="L106" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -6869,31 +6882,31 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
         <v>198</v>
@@ -6901,15 +6914,15 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B5" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -6917,7 +6930,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6925,66 +6938,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B10" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B12" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B13" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B15" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -7006,616 +7019,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B3" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C3" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D3" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E3" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F3" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B5" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C5" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E5" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B7" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F7" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B8" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C8" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D8" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E8" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F8" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C10" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D10" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F10" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B11" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C11" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D11" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E11" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F11" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B12" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C12" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D12" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E12" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F12" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B13" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C13" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D13" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E13" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F13" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B15" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C15" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D15" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F15" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B16" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C16" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D16" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E16" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F16" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B17" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C17" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E17" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F17" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B18" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C18" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D18" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E18" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F18" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B19" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C19" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D19" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E19" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F19" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B20" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C20" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D20" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E20" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="F20" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B21" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C21" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D21" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E21" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F21" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B22" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C22" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D22" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E22" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F22" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B23" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D23" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E23" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F23" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B24" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C24" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D24" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E24" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F24" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B25" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="D25" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E25" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F25" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B26" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C26" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="D26" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B27" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C27" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D27" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E27" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F27" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B28" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C28" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D28" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="E28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F28" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="E29" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F29" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B30" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C30" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D30" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E30" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F30" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B31" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C31" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D31" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="524">
   <si>
     <t>ID</t>
   </si>
@@ -285,6 +285,9 @@
     <t>整间手术室的震颤渐渐平息下来，惨白的灯光不再疯狂闪烁，只是依旧带着嗡嗡的电流声悬在你们头顶。</t>
   </si>
   <si>
+    <t>17 enhanced_suspense-tense-background-music</t>
+  </si>
+  <si>
     <t>bgfade(sntzm_final(2)_88,1)</t>
   </si>
   <si>
@@ -519,6 +522,9 @@
     <t>这不应该......</t>
   </si>
   <si>
+    <t>9 enhanced suspense tensions</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Sophia; 层级=43</t>
   </si>
   <si>
@@ -540,6 +546,38 @@
     <t>源类型=type:txt_pb; 层级=45</t>
   </si>
   <si>
+    <t>如果亚波伦没有撒谎，在他消散的那一刻，这个梦境就应该随之一起崩塌才对，可我感受不到任何波动，整个梦境的锚点还牢牢立在这周围。</t>
+  </si>
+  <si>
+    <r>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_Sophia; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=114</t>
+    </r>
+  </si>
+  <si>
     <t>96</t>
   </si>
   <si>
@@ -691,6 +729,12 @@
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=60</t>
+  </si>
+  <si>
+    <t>正当你们以为这又是他布置的某种陷阱时，脚下的地面却突然剧烈震颤起来，四周的墙壁开始以肉眼可见的速度开裂、剥落，像一团被揉碎的废纸，一点点向内坍缩。</t>
+  </si>
+  <si>
+    <t>5 enhanced leberch-suspense</t>
   </si>
   <si>
     <t>111</t>
@@ -2838,7 +2882,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3646,7 +3690,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" ht="40.5" spans="1:12">
+    <row r="22" ht="60" spans="1:12">
       <c r="A22" t="s">
         <v>81</v>
       </c>
@@ -3672,21 +3716,21 @@
         <v>15</v>
       </c>
       <c r="I22" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="J22" t="s">
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="43.5" spans="1:12">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3704,7 +3748,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3719,12 +3763,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" ht="54" spans="1:12">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3742,7 +3786,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3754,18 +3798,18 @@
         <v>15</v>
       </c>
       <c r="K24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -3780,7 +3824,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3795,12 +3839,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="27" spans="1:12">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3818,7 +3862,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3833,12 +3877,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" ht="42" spans="1:12">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3856,7 +3900,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3871,12 +3915,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="27" spans="1:12">
       <c r="A28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3894,7 +3938,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3909,12 +3953,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="54" spans="1:12">
       <c r="A29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3932,7 +3976,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3947,12 +3991,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" t="s">
         <v>50</v>
@@ -3970,7 +4014,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3985,12 +4029,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -4008,7 +4052,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -4023,12 +4067,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" ht="27" spans="1:12">
       <c r="A32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B32" t="s">
         <v>50</v>
@@ -4046,7 +4090,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4061,12 +4105,12 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="33" ht="40.5" spans="1:12">
       <c r="A33" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4084,7 +4128,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4099,15 +4143,15 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" t="s">
         <v>14</v>
@@ -4122,7 +4166,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4137,12 +4181,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" ht="54" spans="1:12">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4160,7 +4204,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4175,12 +4219,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" ht="54" spans="1:12">
       <c r="A36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4198,7 +4242,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4210,21 +4254,21 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" ht="30" spans="1:12">
       <c r="A37" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -4233,7 +4277,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4245,15 +4289,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="38" ht="27" spans="1:12">
       <c r="A38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4262,7 +4306,7 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E38" t="s">
         <v>15</v>
@@ -4271,7 +4315,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4286,21 +4330,21 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C39" t="s">
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E39" t="s">
         <v>15</v>
@@ -4309,7 +4353,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4324,12 +4368,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" ht="55.5" spans="1:12">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4338,7 +4382,7 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E40" t="s">
         <v>15</v>
@@ -4347,7 +4391,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4362,21 +4406,21 @@
         <v>37</v>
       </c>
       <c r="L40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C41" t="s">
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E41" t="s">
         <v>15</v>
@@ -4385,7 +4429,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4397,15 +4441,15 @@
         <v>15</v>
       </c>
       <c r="K41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4414,7 +4458,7 @@
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E42" t="s">
         <v>15</v>
@@ -4423,7 +4467,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4438,21 +4482,21 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" ht="28.5" spans="1:12">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C43" t="s">
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E43" t="s">
         <v>15</v>
@@ -4461,7 +4505,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4476,12 +4520,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" ht="54" spans="1:12">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4490,7 +4534,7 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E44" t="s">
         <v>15</v>
@@ -4499,7 +4543,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4514,21 +4558,21 @@
         <v>37</v>
       </c>
       <c r="L44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" ht="30" spans="1:12">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4537,27 +4581,27 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>15</v>
+        <v>162</v>
       </c>
       <c r="J45" t="s">
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L45" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
@@ -4566,7 +4610,7 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4575,7 +4619,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4590,12 +4634,12 @@
         <v>37</v>
       </c>
       <c r="L46" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="47" ht="27" spans="1:12">
       <c r="A47" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4613,7 +4657,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4628,59 +4672,44 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12">
-      <c r="A48" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="48" ht="40.5" spans="1:12">
+      <c r="A48">
+        <v>114</v>
       </c>
       <c r="B48" t="s">
+        <v>159</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48" t="s">
+        <v>160</v>
+      </c>
+      <c r="G48" t="s">
+        <v>170</v>
+      </c>
+      <c r="K48" t="s">
+        <v>147</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" t="s">
+        <v>172</v>
+      </c>
+      <c r="B49" t="s">
         <v>50</v>
       </c>
-      <c r="C48" t="s">
-        <v>14</v>
-      </c>
-      <c r="D48" t="s">
-        <v>15</v>
-      </c>
-      <c r="E48" t="s">
-        <v>15</v>
-      </c>
-      <c r="F48" t="s">
-        <v>15</v>
-      </c>
-      <c r="G48" t="s">
-        <v>169</v>
-      </c>
-      <c r="H48" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" t="s">
-        <v>15</v>
-      </c>
-      <c r="J48" t="s">
-        <v>15</v>
-      </c>
-      <c r="K48" t="s">
-        <v>15</v>
-      </c>
-      <c r="L48" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="49" ht="54" spans="1:12">
-      <c r="A49" t="s">
-        <v>171</v>
-      </c>
-      <c r="B49" t="s">
-        <v>158</v>
-      </c>
       <c r="C49" t="s">
         <v>14</v>
       </c>
       <c r="D49" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="E49" t="s">
         <v>15</v>
@@ -4689,7 +4718,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4701,109 +4730,109 @@
         <v>15</v>
       </c>
       <c r="K49" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="L49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s">
+        <v>159</v>
+      </c>
+      <c r="C50" t="s">
+        <v>14</v>
+      </c>
+      <c r="D50" t="s">
+        <v>160</v>
+      </c>
+      <c r="E50" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" t="s">
+        <v>15</v>
+      </c>
+      <c r="G50" t="s">
+        <v>176</v>
+      </c>
+      <c r="H50" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" t="s">
+        <v>15</v>
+      </c>
+      <c r="J50" t="s">
+        <v>15</v>
+      </c>
+      <c r="K50" t="s">
+        <v>147</v>
+      </c>
+      <c r="L50" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" ht="54" spans="1:12">
+      <c r="A51" t="s">
+        <v>178</v>
+      </c>
+      <c r="B51" t="s">
         <v>13</v>
       </c>
-      <c r="C50" t="s">
-        <v>14</v>
-      </c>
-      <c r="D50" t="s">
-        <v>159</v>
-      </c>
-      <c r="E50" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" t="s">
-        <v>15</v>
-      </c>
-      <c r="G50" t="s">
-        <v>175</v>
-      </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" t="s">
-        <v>15</v>
-      </c>
-      <c r="J50" t="s">
-        <v>15</v>
-      </c>
-      <c r="K50" t="s">
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51" t="s">
+        <v>160</v>
+      </c>
+      <c r="E51" t="s">
+        <v>15</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+      <c r="G51" t="s">
+        <v>179</v>
+      </c>
+      <c r="H51" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" t="s">
         <v>37</v>
       </c>
-      <c r="L50" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12">
-      <c r="A51" t="s">
-        <v>177</v>
-      </c>
-      <c r="B51" t="s">
-        <v>121</v>
-      </c>
-      <c r="C51" t="s">
-        <v>14</v>
-      </c>
-      <c r="D51" t="s">
-        <v>131</v>
-      </c>
-      <c r="E51" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" t="s">
-        <v>15</v>
-      </c>
-      <c r="G51" t="s">
-        <v>178</v>
-      </c>
-      <c r="H51" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" t="s">
-        <v>15</v>
-      </c>
-      <c r="J51" t="s">
-        <v>15</v>
-      </c>
-      <c r="K51" t="s">
-        <v>146</v>
-      </c>
       <c r="L51" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="52" ht="30" spans="1:12">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E52" t="s">
         <v>15</v>
       </c>
       <c r="F52" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4815,30 +4844,30 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="L52" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="53" ht="40.5" spans="1:12">
+    <row r="53" ht="30" spans="1:12">
       <c r="A53" t="s">
         <v>184</v>
       </c>
       <c r="B53" t="s">
-        <v>13</v>
+        <v>159</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
       </c>
       <c r="D53" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="E53" t="s">
         <v>15</v>
       </c>
       <c r="F53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G53" t="s">
         <v>185</v>
@@ -4859,7 +4888,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
         <v>188</v>
       </c>
@@ -4876,7 +4905,7 @@
         <v>15</v>
       </c>
       <c r="F54" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="G54" t="s">
         <v>189</v>
@@ -4891,62 +4920,62 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>15</v>
+        <v>190</v>
       </c>
       <c r="L54" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="55" ht="30" spans="1:12">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="C55" t="s">
         <v>14</v>
       </c>
       <c r="D55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E55" t="s">
+        <v>15</v>
+      </c>
+      <c r="F55" t="s">
+        <v>15</v>
+      </c>
+      <c r="G55" t="s">
+        <v>193</v>
+      </c>
+      <c r="H55" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" t="s">
+        <v>15</v>
+      </c>
+      <c r="J55" t="s">
+        <v>15</v>
+      </c>
+      <c r="K55" t="s">
+        <v>15</v>
+      </c>
+      <c r="L55" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56" ht="30" spans="1:12">
+      <c r="A56" t="s">
+        <v>195</v>
+      </c>
+      <c r="B56" t="s">
         <v>159</v>
       </c>
-      <c r="E55" t="s">
-        <v>15</v>
-      </c>
-      <c r="F55" t="s">
-        <v>15</v>
-      </c>
-      <c r="G55" t="s">
-        <v>192</v>
-      </c>
-      <c r="H55" t="s">
-        <v>15</v>
-      </c>
-      <c r="I55" t="s">
-        <v>15</v>
-      </c>
-      <c r="J55" t="s">
-        <v>15</v>
-      </c>
-      <c r="K55" t="s">
-        <v>146</v>
-      </c>
-      <c r="L55" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="56" ht="40.5" spans="1:12">
-      <c r="A56" t="s">
-        <v>194</v>
-      </c>
-      <c r="B56" t="s">
-        <v>13</v>
-      </c>
       <c r="C56" t="s">
         <v>14</v>
       </c>
       <c r="D56" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E56" t="s">
         <v>15</v>
@@ -4955,7 +4984,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4967,147 +4996,147 @@
         <v>15</v>
       </c>
       <c r="K56" t="s">
-        <v>196</v>
+        <v>147</v>
       </c>
       <c r="L56" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
         <v>198</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
         <v>14</v>
       </c>
       <c r="D57" t="s">
+        <v>160</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" t="s">
+        <v>15</v>
+      </c>
+      <c r="G57" t="s">
         <v>199</v>
       </c>
-      <c r="E57" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" t="s">
-        <v>15</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="H57" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" t="s">
+        <v>15</v>
+      </c>
+      <c r="J57" t="s">
+        <v>15</v>
+      </c>
+      <c r="K57" t="s">
         <v>200</v>
-      </c>
-      <c r="H57" t="s">
-        <v>15</v>
-      </c>
-      <c r="I57" t="s">
-        <v>15</v>
-      </c>
-      <c r="J57" t="s">
-        <v>15</v>
-      </c>
-      <c r="K57" t="s">
-        <v>146</v>
       </c>
       <c r="L57" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="58" ht="40.5" spans="1:12">
+    <row r="58" spans="1:12">
       <c r="A58" t="s">
         <v>202</v>
       </c>
       <c r="B58" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" t="s">
+        <v>14</v>
+      </c>
+      <c r="D58" t="s">
+        <v>203</v>
+      </c>
+      <c r="E58" t="s">
+        <v>15</v>
+      </c>
+      <c r="F58" t="s">
+        <v>15</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="H58" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" t="s">
+        <v>147</v>
+      </c>
+      <c r="L58" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="59" ht="40.5" spans="1:12">
+      <c r="A59" t="s">
+        <v>206</v>
+      </c>
+      <c r="B59" t="s">
         <v>13</v>
       </c>
-      <c r="C58" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" t="s">
-        <v>199</v>
-      </c>
-      <c r="E58" t="s">
-        <v>15</v>
-      </c>
-      <c r="F58" t="s">
-        <v>15</v>
-      </c>
-      <c r="G58" t="s">
+      <c r="C59" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" t="s">
         <v>203</v>
       </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>15</v>
-      </c>
-      <c r="J58" t="s">
-        <v>15</v>
-      </c>
-      <c r="K58" t="s">
+      <c r="E59" t="s">
+        <v>15</v>
+      </c>
+      <c r="F59" t="s">
+        <v>15</v>
+      </c>
+      <c r="G59" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" t="s">
+        <v>15</v>
+      </c>
+      <c r="K59" t="s">
         <v>37</v>
       </c>
-      <c r="L58" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="59" ht="30" spans="1:12">
-      <c r="A59" t="s">
-        <v>205</v>
-      </c>
-      <c r="B59" t="s">
-        <v>158</v>
-      </c>
-      <c r="C59" t="s">
-        <v>14</v>
-      </c>
-      <c r="D59" t="s">
-        <v>159</v>
-      </c>
-      <c r="E59" t="s">
-        <v>15</v>
-      </c>
-      <c r="F59" t="s">
-        <v>15</v>
-      </c>
-      <c r="G59" t="s">
-        <v>206</v>
-      </c>
-      <c r="H59" t="s">
-        <v>15</v>
-      </c>
-      <c r="I59" t="s">
-        <v>15</v>
-      </c>
-      <c r="J59" t="s">
-        <v>15</v>
-      </c>
-      <c r="K59" t="s">
-        <v>146</v>
-      </c>
       <c r="L59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" ht="30" spans="1:12">
       <c r="A60" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C60" t="s">
         <v>14</v>
       </c>
       <c r="D60" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E60" t="s">
         <v>15</v>
       </c>
       <c r="F60" t="s">
-        <v>131</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5119,30 +5148,30 @@
         <v>15</v>
       </c>
       <c r="K60" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="L60" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="61" ht="27" spans="1:12">
+    <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
         <v>212</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>122</v>
       </c>
       <c r="C61" t="s">
         <v>14</v>
       </c>
       <c r="D61" t="s">
-        <v>15</v>
+        <v>160</v>
       </c>
       <c r="E61" t="s">
         <v>15</v>
       </c>
       <c r="F61" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G61" t="s">
         <v>213</v>
@@ -5157,15 +5186,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>186</v>
+        <v>214</v>
       </c>
       <c r="L61" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="62" ht="40.5" spans="1:12">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="62" ht="27" spans="1:12">
       <c r="A62" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5180,10 +5209,10 @@
         <v>15</v>
       </c>
       <c r="F62" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="G62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5195,18 +5224,18 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L62" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
         <v>219</v>
       </c>
       <c r="B63" t="s">
-        <v>158</v>
+        <v>13</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
@@ -5233,56 +5262,35 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>15</v>
+        <v>221</v>
       </c>
       <c r="L63" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12">
-      <c r="A64" t="s">
         <v>222</v>
       </c>
+    </row>
+    <row r="64" ht="54" spans="1:12">
+      <c r="A64">
+        <v>115</v>
+      </c>
       <c r="B64" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
-      </c>
-      <c r="D64" t="s">
-        <v>15</v>
-      </c>
-      <c r="E64" t="s">
-        <v>15</v>
-      </c>
-      <c r="F64" t="s">
-        <v>15</v>
       </c>
       <c r="G64" t="s">
         <v>223</v>
       </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
       <c r="I64" t="s">
-        <v>15</v>
-      </c>
-      <c r="J64" t="s">
-        <v>15</v>
-      </c>
-      <c r="K64" t="s">
-        <v>15</v>
-      </c>
-      <c r="L64" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="65" ht="30" spans="1:12">
+    <row r="65" spans="1:12">
       <c r="A65" t="s">
         <v>225</v>
       </c>
       <c r="B65" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="C65" t="s">
         <v>14</v>
@@ -5308,16 +5316,16 @@
       <c r="J65" t="s">
         <v>15</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="K65" t="s">
+        <v>15</v>
+      </c>
+      <c r="L65" t="s">
         <v>227</v>
       </c>
-      <c r="L65" t="s">
+    </row>
+    <row r="66" spans="1:12">
+      <c r="A66" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="66" ht="54" spans="1:12">
-      <c r="A66" t="s">
-        <v>229</v>
       </c>
       <c r="B66" t="s">
         <v>50</v>
@@ -5335,74 +5343,74 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
+        <v>229</v>
+      </c>
+      <c r="H66" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" t="s">
         <v>230</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J66" t="s">
-        <v>15</v>
-      </c>
-      <c r="K66" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
+        <v>231</v>
+      </c>
+      <c r="B67" t="s">
+        <v>122</v>
+      </c>
+      <c r="C67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D67" t="s">
+        <v>15</v>
+      </c>
+      <c r="E67" t="s">
+        <v>15</v>
+      </c>
+      <c r="F67" t="s">
+        <v>15</v>
+      </c>
+      <c r="G67" t="s">
         <v>232</v>
       </c>
-      <c r="B67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" t="s">
-        <v>14</v>
-      </c>
-      <c r="D67" t="s">
-        <v>26</v>
-      </c>
-      <c r="E67" t="s">
-        <v>15</v>
-      </c>
-      <c r="F67" t="s">
-        <v>15</v>
-      </c>
-      <c r="G67" t="s">
+      <c r="H67" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" t="s">
+        <v>15</v>
+      </c>
+      <c r="J67" t="s">
+        <v>15</v>
+      </c>
+      <c r="K67" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H67" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" t="s">
-        <v>15</v>
-      </c>
-      <c r="J67" t="s">
-        <v>15</v>
-      </c>
-      <c r="K67" t="s">
-        <v>146</v>
-      </c>
       <c r="L67" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="68" ht="30" spans="1:12">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="68" ht="54" spans="1:12">
       <c r="A68" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B68" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C68" t="s">
         <v>14</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E68" t="s">
         <v>15</v>
@@ -5411,7 +5419,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5426,12 +5434,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="69" ht="55.5" spans="1:12">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
@@ -5449,7 +5457,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5461,10 +5469,10 @@
         <v>15</v>
       </c>
       <c r="K69" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="L69" t="s">
-        <v>239</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" ht="30" spans="1:12">
@@ -5472,7 +5480,7 @@
         <v>240</v>
       </c>
       <c r="B70" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C70" t="s">
         <v>14</v>
@@ -5505,7 +5513,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="71" ht="54" spans="1:12">
+    <row r="71" ht="55.5" spans="1:12">
       <c r="A71" t="s">
         <v>243</v>
       </c>
@@ -5543,12 +5551,12 @@
         <v>245</v>
       </c>
     </row>
-    <row r="72" ht="42" spans="1:12">
+    <row r="72" ht="30" spans="1:12">
       <c r="A72" t="s">
         <v>246</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C72" t="s">
         <v>14</v>
@@ -5578,12 +5586,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="73" ht="67.5" spans="1:12">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="73" ht="54" spans="1:12">
       <c r="A73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
@@ -5601,7 +5609,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5616,15 +5624,15 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="74" ht="30" spans="1:12">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="74" ht="42" spans="1:12">
       <c r="A74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B74" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
         <v>14</v>
@@ -5639,7 +5647,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5651,10 +5659,10 @@
         <v>15</v>
       </c>
       <c r="K74" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>253</v>
+        <v>42</v>
       </c>
     </row>
     <row r="75" ht="67.5" spans="1:12">
@@ -5662,13 +5670,13 @@
         <v>254</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C75" t="s">
         <v>14</v>
       </c>
       <c r="D75" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E75" t="s">
         <v>15</v>
@@ -5695,12 +5703,12 @@
         <v>256</v>
       </c>
     </row>
-    <row r="76" ht="54" spans="1:12">
+    <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
         <v>257</v>
       </c>
       <c r="B76" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C76" t="s">
         <v>14</v>
@@ -5727,56 +5735,56 @@
         <v>15</v>
       </c>
       <c r="K76" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="L76" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="77" ht="42" spans="1:12">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="77" ht="67.5" spans="1:12">
       <c r="A77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B77" t="s">
+        <v>13</v>
+      </c>
+      <c r="C77" t="s">
+        <v>14</v>
+      </c>
+      <c r="D77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E77" t="s">
+        <v>15</v>
+      </c>
+      <c r="F77" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" t="s">
+        <v>261</v>
+      </c>
+      <c r="H77" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" t="s">
+        <v>15</v>
+      </c>
+      <c r="J77" t="s">
+        <v>15</v>
+      </c>
+      <c r="K77" t="s">
+        <v>15</v>
+      </c>
+      <c r="L77" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="78" ht="54" spans="1:12">
+      <c r="A78" t="s">
+        <v>263</v>
+      </c>
+      <c r="B78" t="s">
         <v>22</v>
-      </c>
-      <c r="C77" t="s">
-        <v>14</v>
-      </c>
-      <c r="D77" t="s">
-        <v>26</v>
-      </c>
-      <c r="E77" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" t="s">
-        <v>260</v>
-      </c>
-      <c r="H77" t="s">
-        <v>15</v>
-      </c>
-      <c r="I77" t="s">
-        <v>15</v>
-      </c>
-      <c r="J77" t="s">
-        <v>15</v>
-      </c>
-      <c r="K77" t="s">
-        <v>15</v>
-      </c>
-      <c r="L77" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="78" ht="30" spans="1:12">
-      <c r="A78" t="s">
-        <v>262</v>
-      </c>
-      <c r="B78" t="s">
-        <v>13</v>
       </c>
       <c r="C78" t="s">
         <v>14</v>
@@ -5791,7 +5799,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5803,13 +5811,13 @@
         <v>15</v>
       </c>
       <c r="K78" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="L78" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="79" ht="69" spans="1:12">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="79" ht="42" spans="1:12">
       <c r="A79" t="s">
         <v>265</v>
       </c>
@@ -5844,15 +5852,15 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>64</v>
+        <v>267</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B80" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -5867,7 +5875,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5879,15 +5887,15 @@
         <v>15</v>
       </c>
       <c r="K80" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="81" ht="30" spans="1:12">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="81" ht="69" spans="1:12">
       <c r="A81" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B81" t="s">
         <v>22</v>
@@ -5905,7 +5913,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5917,18 +5925,18 @@
         <v>15</v>
       </c>
       <c r="K81" t="s">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="82" ht="40.5" spans="1:12">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" ht="30" spans="1:12">
       <c r="A82" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B82" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="C82" t="s">
         <v>14</v>
@@ -5943,7 +5951,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5955,15 +5963,15 @@
         <v>15</v>
       </c>
       <c r="K82" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L82" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="83" ht="42" spans="1:12">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="83" ht="30" spans="1:12">
       <c r="A83" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B83" t="s">
         <v>22</v>
@@ -5981,7 +5989,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5992,13 +6000,16 @@
       <c r="J83" t="s">
         <v>15</v>
       </c>
+      <c r="K83" t="s">
+        <v>147</v>
+      </c>
       <c r="L83" t="s">
-        <v>276</v>
+        <v>71</v>
       </c>
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6016,7 +6027,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6031,12 +6042,12 @@
         <v>15</v>
       </c>
       <c r="L84" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" ht="42" spans="1:12">
       <c r="A85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B85" t="s">
         <v>22</v>
@@ -6054,7 +6065,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6065,19 +6076,16 @@
       <c r="J85" t="s">
         <v>15</v>
       </c>
-      <c r="K85" t="s">
-        <v>15</v>
-      </c>
       <c r="L85" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="86" ht="30" spans="1:12">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B86" t="s">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C86" t="s">
         <v>14</v>
@@ -6092,7 +6100,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6104,13 +6112,13 @@
         <v>15</v>
       </c>
       <c r="K86" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="87" ht="40.5" spans="1:12">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="87" ht="42" spans="1:12">
       <c r="A87" t="s">
         <v>285</v>
       </c>
@@ -6142,7 +6150,7 @@
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>146</v>
+        <v>15</v>
       </c>
       <c r="L87" t="s">
         <v>287</v>
@@ -6153,7 +6161,7 @@
         <v>288</v>
       </c>
       <c r="B88" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
@@ -6180,18 +6188,18 @@
         <v>15</v>
       </c>
       <c r="K88" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="L88" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="89" ht="30" spans="1:12">
+    <row r="89" ht="40.5" spans="1:12">
       <c r="A89" t="s">
         <v>291</v>
       </c>
       <c r="B89" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C89" t="s">
         <v>14</v>
@@ -6218,15 +6226,15 @@
         <v>15</v>
       </c>
       <c r="K89" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="L89" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="90" ht="40.5" spans="1:12">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="90" ht="30" spans="1:12">
       <c r="A90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
@@ -6244,7 +6252,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6259,15 +6267,15 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="91" ht="30" spans="1:12">
       <c r="A91" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B91" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C91" t="s">
         <v>14</v>
@@ -6282,7 +6290,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6297,15 +6305,15 @@
         <v>15</v>
       </c>
       <c r="L91" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="92" ht="55.5" spans="1:12">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="92" ht="40.5" spans="1:12">
       <c r="A92" t="s">
         <v>299</v>
       </c>
       <c r="B92" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C92" t="s">
         <v>14</v>
@@ -6332,53 +6340,56 @@
         <v>15</v>
       </c>
       <c r="K92" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="93" ht="67.5" spans="1:12">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="93" ht="30" spans="1:12">
       <c r="A93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B93" t="s">
+        <v>22</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" t="s">
+        <v>15</v>
+      </c>
+      <c r="F93" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" t="s">
+        <v>303</v>
+      </c>
+      <c r="H93" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" t="s">
+        <v>15</v>
+      </c>
+      <c r="J93" t="s">
+        <v>15</v>
+      </c>
+      <c r="K93" t="s">
+        <v>15</v>
+      </c>
+      <c r="L93" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="94" ht="55.5" spans="1:12">
+      <c r="A94" t="s">
+        <v>305</v>
+      </c>
+      <c r="B94" t="s">
         <v>13</v>
-      </c>
-      <c r="C93" t="s">
-        <v>14</v>
-      </c>
-      <c r="E93" t="s">
-        <v>15</v>
-      </c>
-      <c r="F93" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" t="s">
-        <v>302</v>
-      </c>
-      <c r="H93" t="s">
-        <v>15</v>
-      </c>
-      <c r="I93" t="s">
-        <v>15</v>
-      </c>
-      <c r="J93" t="s">
-        <v>15</v>
-      </c>
-      <c r="K93" t="s">
-        <v>15</v>
-      </c>
-      <c r="L93" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="94" ht="54" spans="1:12">
-      <c r="A94" t="s">
-        <v>304</v>
-      </c>
-      <c r="B94" t="s">
-        <v>22</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -6393,7 +6404,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6405,30 +6416,27 @@
         <v>15</v>
       </c>
       <c r="K94" t="s">
-        <v>146</v>
+        <v>37</v>
       </c>
       <c r="L94" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="95" ht="54" spans="1:12">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="95" ht="67.5" spans="1:12">
       <c r="A95" t="s">
         <v>307</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>13</v>
       </c>
       <c r="C95" t="s">
         <v>14</v>
       </c>
-      <c r="D95" t="s">
-        <v>26</v>
-      </c>
       <c r="E95" t="s">
         <v>15</v>
       </c>
       <c r="F95" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="G95" t="s">
         <v>308</v>
@@ -6443,30 +6451,30 @@
         <v>15</v>
       </c>
       <c r="K95" t="s">
-        <v>210</v>
+        <v>15</v>
       </c>
       <c r="L95" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="96" ht="40.5" spans="1:12">
+    <row r="96" ht="54" spans="1:12">
       <c r="A96" t="s">
         <v>310</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C96" t="s">
         <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E96" t="s">
         <v>15</v>
       </c>
       <c r="F96" t="s">
-        <v>199</v>
+        <v>15</v>
       </c>
       <c r="G96" t="s">
         <v>311</v>
@@ -6481,18 +6489,18 @@
         <v>15</v>
       </c>
       <c r="K96" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="L96" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="97" ht="42" spans="1:12">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="97" ht="54" spans="1:12">
       <c r="A97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B97" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="C97" t="s">
         <v>14</v>
@@ -6504,10 +6512,10 @@
         <v>15</v>
       </c>
       <c r="F97" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
       <c r="G97" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6519,15 +6527,15 @@
         <v>15</v>
       </c>
       <c r="K97" t="s">
-        <v>146</v>
+        <v>214</v>
       </c>
       <c r="L97" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="98" ht="69" spans="1:12">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6536,16 +6544,16 @@
         <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="E98" t="s">
         <v>15</v>
       </c>
       <c r="F98" t="s">
-        <v>15</v>
+        <v>203</v>
       </c>
       <c r="G98" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6557,13 +6565,13 @@
         <v>15</v>
       </c>
       <c r="K98" t="s">
-        <v>317</v>
+        <v>190</v>
       </c>
       <c r="L98" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="99" ht="40.5" spans="1:12">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="99" ht="42" spans="1:12">
       <c r="A99" t="s">
         <v>318</v>
       </c>
@@ -6595,18 +6603,18 @@
         <v>15</v>
       </c>
       <c r="K99" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L99" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="100" ht="30" spans="1:12">
+    <row r="100" ht="69" spans="1:12">
       <c r="A100" t="s">
         <v>321</v>
       </c>
       <c r="B100" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C100" t="s">
         <v>14</v>
@@ -6632,8 +6640,11 @@
       <c r="J100" t="s">
         <v>15</v>
       </c>
+      <c r="K100" t="s">
+        <v>323</v>
+      </c>
       <c r="L100" t="s">
-        <v>323</v>
+        <v>127</v>
       </c>
     </row>
     <row r="101" ht="40.5" spans="1:12">
@@ -6641,7 +6652,7 @@
         <v>324</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
@@ -6668,15 +6679,15 @@
         <v>15</v>
       </c>
       <c r="K101" t="s">
-        <v>15</v>
+        <v>147</v>
       </c>
       <c r="L101" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="102" ht="43.5" spans="1:12">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="102" ht="30" spans="1:12">
       <c r="A102" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
@@ -6694,7 +6705,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6705,19 +6716,16 @@
       <c r="J102" t="s">
         <v>15</v>
       </c>
-      <c r="K102" t="s">
-        <v>15</v>
-      </c>
       <c r="L102" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="103" ht="54" spans="1:12">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="103" ht="40.5" spans="1:12">
       <c r="A103" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B103" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
         <v>14</v>
@@ -6732,7 +6740,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6747,10 +6755,10 @@
         <v>15</v>
       </c>
       <c r="L103" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="104" ht="30" spans="1:12">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="104" ht="43.5" spans="1:12">
       <c r="A104" t="s">
         <v>332</v>
       </c>
@@ -6788,12 +6796,12 @@
         <v>334</v>
       </c>
     </row>
-    <row r="105" ht="55.5" spans="1:12">
+    <row r="105" ht="54" spans="1:12">
       <c r="A105" t="s">
         <v>335</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C105" t="s">
         <v>14</v>
@@ -6820,24 +6828,24 @@
         <v>15</v>
       </c>
       <c r="K105" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="L105" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" ht="40.5" spans="1:12">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="106" ht="30" spans="1:12">
       <c r="A106" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C106" t="s">
         <v>14</v>
       </c>
       <c r="D106" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E106" t="s">
         <v>15</v>
@@ -6846,7 +6854,7 @@
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H106" t="s">
         <v>15</v>
@@ -6857,11 +6865,87 @@
       <c r="J106" t="s">
         <v>15</v>
       </c>
-      <c r="K106" s="3" t="s">
-        <v>339</v>
+      <c r="K106" t="s">
+        <v>15</v>
       </c>
       <c r="L106" t="s">
         <v>340</v>
+      </c>
+    </row>
+    <row r="107" ht="55.5" spans="1:12">
+      <c r="A107" t="s">
+        <v>341</v>
+      </c>
+      <c r="B107" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" t="s">
+        <v>14</v>
+      </c>
+      <c r="D107" t="s">
+        <v>26</v>
+      </c>
+      <c r="E107" t="s">
+        <v>15</v>
+      </c>
+      <c r="F107" t="s">
+        <v>15</v>
+      </c>
+      <c r="G107" t="s">
+        <v>342</v>
+      </c>
+      <c r="H107" t="s">
+        <v>15</v>
+      </c>
+      <c r="I107" t="s">
+        <v>15</v>
+      </c>
+      <c r="J107" t="s">
+        <v>15</v>
+      </c>
+      <c r="K107" t="s">
+        <v>37</v>
+      </c>
+      <c r="L107" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="108" ht="40.5" spans="1:12">
+      <c r="A108" t="s">
+        <v>343</v>
+      </c>
+      <c r="B108" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108" t="s">
+        <v>15</v>
+      </c>
+      <c r="E108" t="s">
+        <v>15</v>
+      </c>
+      <c r="F108" t="s">
+        <v>15</v>
+      </c>
+      <c r="G108" t="s">
+        <v>344</v>
+      </c>
+      <c r="H108" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" t="s">
+        <v>15</v>
+      </c>
+      <c r="J108" t="s">
+        <v>15</v>
+      </c>
+      <c r="K108" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="L108" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -6882,47 +6966,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B2" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B3" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B5" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -6930,7 +7014,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -6938,66 +7022,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B8" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B9" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B10" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B11" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B12" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B13" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B14" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B15" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -7019,616 +7103,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B2" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="E2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="F2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="C3" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="D3" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="E3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="F3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B4" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C4" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="D4" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E4" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="F4" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B5" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D5" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="E5" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F5" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B6" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C6" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D6" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="E6" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="F6" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B7" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="C7" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="D7" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="E7" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="F7" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B8" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="C8" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="D8" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="E8" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="F8" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B9" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C9" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="D9" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="E9" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="F9" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B10" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C10" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="D10" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="E10" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="F10" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B11" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C11" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D11" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="E11" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="F11" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B12" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="C12" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="D12" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E12" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="F12" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B13" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C13" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="D13" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="E13" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F13" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B14" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C14" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="D14" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E14" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F14" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B15" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C15" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="D15" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="E15" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="F15" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B16" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C16" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="D16" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="E16" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F16" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B17" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C17" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="D17" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="E17" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="F17" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B18" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C18" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="D18" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="E18" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F18" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B19" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C19" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="D19" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="E19" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F19" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B20" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C20" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="D20" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="E20" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="F20" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B21" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C21" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D21" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="E21" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="F21" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B22" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C22" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="D22" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="E22" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F22" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B23" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C23" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="D23" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="E23" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="F23" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B24" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="C24" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="D24" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="E24" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="F24" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B25" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C25" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="D25" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="E25" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="F25" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B26" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C26" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="D26" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="E26" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F26" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B27" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C27" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="D27" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E27" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="F27" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B28" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C28" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="D28" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="E28" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="F28" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B29" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C29" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="D29" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="E29" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F29" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="B30" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C30" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="D30" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="E30" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="F30" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B31" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C31" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="D31" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_final(3).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_终局（下）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1492" uniqueCount="526">
   <si>
     <t>ID</t>
   </si>
@@ -288,7 +288,7 @@
     <t>17 enhanced_suspense-tense-background-music</t>
   </si>
   <si>
-    <t>bgfade(sntzm_final(2)_88,1)</t>
+    <t>bgfade(sntzm_final(2)_88,1)&amp;unlockmusic(Music17)</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=20</t>
@@ -525,6 +525,9 @@
     <t>9 enhanced suspense tensions</t>
   </si>
   <si>
+    <t>charfadein(L,1)&amp;unlockmusic(Music9)</t>
+  </si>
+  <si>
     <t>源类型=type:txt_Sophia; 层级=43</t>
   </si>
   <si>
@@ -550,6 +553,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -735,6 +743,9 @@
   </si>
   <si>
     <t>5 enhanced leberch-suspense</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music5)</t>
   </si>
   <si>
     <t>111</t>
@@ -4593,15 +4604,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="L45" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B46" t="s">
         <v>50</v>
@@ -4619,7 +4630,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4634,12 +4645,12 @@
         <v>37</v>
       </c>
       <c r="L46" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" ht="27" spans="1:12">
       <c r="A47" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" t="s">
         <v>13</v>
@@ -4657,7 +4668,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4672,7 +4683,7 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="48" ht="40.5" spans="1:12">
@@ -4689,18 +4700,18 @@
         <v>160</v>
       </c>
       <c r="G48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K48" t="s">
         <v>147</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
         <v>50</v>
@@ -4718,7 +4729,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4733,12 +4744,12 @@
         <v>37</v>
       </c>
       <c r="L49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" ht="54" spans="1:12">
       <c r="A50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" t="s">
         <v>159</v>
@@ -4756,7 +4767,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4771,12 +4782,12 @@
         <v>147</v>
       </c>
       <c r="L50" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="51" ht="54" spans="1:12">
       <c r="A51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4794,7 +4805,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4809,12 +4820,12 @@
         <v>37</v>
       </c>
       <c r="L51" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" t="s">
         <v>122</v>
@@ -4832,7 +4843,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4847,12 +4858,12 @@
         <v>147</v>
       </c>
       <c r="L52" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="53" ht="30" spans="1:12">
       <c r="A53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B53" t="s">
         <v>159</v>
@@ -4870,7 +4881,7 @@
         <v>160</v>
       </c>
       <c r="G53" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4882,15 +4893,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L53" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="54" ht="40.5" spans="1:12">
       <c r="A54" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4908,7 +4919,7 @@
         <v>160</v>
       </c>
       <c r="G54" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4920,15 +4931,15 @@
         <v>15</v>
       </c>
       <c r="K54" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L54" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4946,7 +4957,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4961,12 +4972,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" ht="30" spans="1:12">
       <c r="A56" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" t="s">
         <v>159</v>
@@ -4984,7 +4995,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4999,12 +5010,12 @@
         <v>147</v>
       </c>
       <c r="L56" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -5022,7 +5033,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -5034,15 +5045,15 @@
         <v>15</v>
       </c>
       <c r="K57" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L57" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B58" t="s">
         <v>94</v>
@@ -5051,7 +5062,7 @@
         <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E58" t="s">
         <v>15</v>
@@ -5060,7 +5071,7 @@
         <v>15</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -5075,12 +5086,12 @@
         <v>147</v>
       </c>
       <c r="L58" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="59" ht="40.5" spans="1:12">
       <c r="A59" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5089,7 +5100,7 @@
         <v>14</v>
       </c>
       <c r="D59" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E59" t="s">
         <v>15</v>
@@ -5098,7 +5109,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5113,12 +5124,12 @@
         <v>37</v>
       </c>
       <c r="L59" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="60" ht="30" spans="1:12">
       <c r="A60" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B60" t="s">
         <v>159</v>
@@ -5136,7 +5147,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5151,12 +5162,12 @@
         <v>147</v>
       </c>
       <c r="L60" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" t="s">
         <v>122</v>
@@ -5174,7 +5185,7 @@
         <v>132</v>
       </c>
       <c r="G61" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5186,15 +5197,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="62" ht="27" spans="1:12">
       <c r="A62" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5212,7 +5223,7 @@
         <v>132</v>
       </c>
       <c r="G62" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5224,15 +5235,15 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L62" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="63" ht="40.5" spans="1:12">
       <c r="A63" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -5250,7 +5261,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5262,10 +5273,10 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L63" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
@@ -5279,15 +5290,18 @@
         <v>14</v>
       </c>
       <c r="G64" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I64" t="s">
-        <v>224</v>
+        <v>225</v>
+      </c>
+      <c r="K64" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B65" t="s">
         <v>159</v>
@@ -5305,7 +5319,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5320,12 +5334,12 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s">
         <v>50</v>
@@ -5343,7 +5357,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5358,12 +5372,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="67" ht="30" spans="1:12">
       <c r="A67" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B67" t="s">
         <v>122</v>
@@ -5381,7 +5395,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5393,15 +5407,15 @@
         <v>15</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L67" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="68" ht="54" spans="1:12">
       <c r="A68" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B68" t="s">
         <v>50</v>
@@ -5419,7 +5433,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5434,12 +5448,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B69" t="s">
         <v>22</v>
@@ -5457,7 +5471,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5477,7 +5491,7 @@
     </row>
     <row r="70" ht="30" spans="1:12">
       <c r="A70" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5495,7 +5509,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5510,12 +5524,12 @@
         <v>15</v>
       </c>
       <c r="L70" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="71" ht="55.5" spans="1:12">
       <c r="A71" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B71" t="s">
         <v>22</v>
@@ -5533,7 +5547,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5548,12 +5562,12 @@
         <v>15</v>
       </c>
       <c r="L71" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="72" ht="30" spans="1:12">
       <c r="A72" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B72" t="s">
         <v>22</v>
@@ -5571,7 +5585,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5586,12 +5600,12 @@
         <v>15</v>
       </c>
       <c r="L72" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="73" ht="54" spans="1:12">
       <c r="A73" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
@@ -5609,7 +5623,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5624,12 +5638,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" ht="42" spans="1:12">
       <c r="A74" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B74" t="s">
         <v>13</v>
@@ -5647,7 +5661,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5667,7 +5681,7 @@
     </row>
     <row r="75" ht="67.5" spans="1:12">
       <c r="A75" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B75" t="s">
         <v>22</v>
@@ -5685,7 +5699,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5700,12 +5714,12 @@
         <v>15</v>
       </c>
       <c r="L75" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="76" ht="30" spans="1:12">
       <c r="A76" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B76" t="s">
         <v>50</v>
@@ -5723,7 +5737,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5738,12 +5752,12 @@
         <v>37</v>
       </c>
       <c r="L76" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="77" ht="67.5" spans="1:12">
       <c r="A77" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5761,7 +5775,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5776,12 +5790,12 @@
         <v>15</v>
       </c>
       <c r="L77" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="78" ht="54" spans="1:12">
       <c r="A78" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B78" t="s">
         <v>22</v>
@@ -5799,7 +5813,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5819,7 +5833,7 @@
     </row>
     <row r="79" ht="42" spans="1:12">
       <c r="A79" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B79" t="s">
         <v>22</v>
@@ -5837,7 +5851,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5852,12 +5866,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="80" ht="30" spans="1:12">
       <c r="A80" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5875,7 +5889,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5890,12 +5904,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="81" ht="69" spans="1:12">
       <c r="A81" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B81" t="s">
         <v>22</v>
@@ -5913,7 +5927,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5933,7 +5947,7 @@
     </row>
     <row r="82" ht="30" spans="1:12">
       <c r="A82" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B82" t="s">
         <v>50</v>
@@ -5951,7 +5965,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5966,12 +5980,12 @@
         <v>37</v>
       </c>
       <c r="L82" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="83" ht="30" spans="1:12">
       <c r="A83" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B83" t="s">
         <v>22</v>
@@ -5989,7 +6003,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -6009,7 +6023,7 @@
     </row>
     <row r="84" ht="40.5" spans="1:12">
       <c r="A84" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -6027,7 +6041,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -6047,7 +6061,7 @@
     </row>
     <row r="85" ht="42" spans="1:12">
       <c r="A85" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B85" t="s">
         <v>22</v>
@@ -6065,7 +6079,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6077,12 +6091,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" ht="40.5" spans="1:12">
       <c r="A86" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6100,7 +6114,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6120,7 +6134,7 @@
     </row>
     <row r="87" ht="42" spans="1:12">
       <c r="A87" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B87" t="s">
         <v>22</v>
@@ -6138,7 +6152,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6153,12 +6167,12 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="88" ht="30" spans="1:12">
       <c r="A88" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B88" t="s">
         <v>50</v>
@@ -6176,7 +6190,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6191,12 +6205,12 @@
         <v>37</v>
       </c>
       <c r="L88" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="89" ht="40.5" spans="1:12">
       <c r="A89" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B89" t="s">
         <v>22</v>
@@ -6214,7 +6228,7 @@
         <v>15</v>
       </c>
       <c r="G89" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="H89" t="s">
         <v>15</v>
@@ -6229,12 +6243,12 @@
         <v>147</v>
       </c>
       <c r="L89" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" ht="30" spans="1:12">
       <c r="A90" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B90" t="s">
         <v>22</v>
@@ -6252,7 +6266,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6267,12 +6281,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="91" ht="30" spans="1:12">
       <c r="A91" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6290,7 +6304,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6310,7 +6324,7 @@
     </row>
     <row r="92" ht="40.5" spans="1:12">
       <c r="A92" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B92" t="s">
         <v>22</v>
@@ -6328,7 +6342,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6343,12 +6357,12 @@
         <v>15</v>
       </c>
       <c r="L92" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="93" ht="30" spans="1:12">
       <c r="A93" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B93" t="s">
         <v>22</v>
@@ -6366,7 +6380,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6381,12 +6395,12 @@
         <v>15</v>
       </c>
       <c r="L93" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="94" ht="55.5" spans="1:12">
       <c r="A94" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6404,7 +6418,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6424,7 +6438,7 @@
     </row>
     <row r="95" ht="67.5" spans="1:12">
       <c r="A95" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6439,7 +6453,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6454,12 +6468,12 @@
         <v>15</v>
       </c>
       <c r="L95" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="96" ht="54" spans="1:12">
       <c r="A96" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B96" t="s">
         <v>22</v>
@@ -6477,7 +6491,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6492,12 +6506,12 @@
         <v>147</v>
       </c>
       <c r="L96" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="97" ht="54" spans="1:12">
       <c r="A97" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B97" t="s">
         <v>94</v>
@@ -6512,10 +6526,10 @@
         <v>15</v>
       </c>
       <c r="F97" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G97" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6527,15 +6541,15 @@
         <v>15</v>
       </c>
       <c r="K97" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L97" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s">
         <v>13</v>
@@ -6550,10 +6564,10 @@
         <v>15</v>
       </c>
       <c r="F98" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G98" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6565,7 +6579,7 @@
         <v>15</v>
       </c>
       <c r="K98" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L98" t="s">
         <v>120</v>
@@ -6573,7 +6587,7 @@
     </row>
     <row r="99" ht="42" spans="1:12">
       <c r="A99" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B99" t="s">
         <v>22</v>
@@ -6591,7 +6605,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6606,12 +6620,12 @@
         <v>147</v>
       </c>
       <c r="L99" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="100" ht="69" spans="1:12">
       <c r="A100" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B100" t="s">
         <v>13</v>
@@ -6629,7 +6643,7 @@
         <v>15</v>
       </c>
       <c r="G100" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="H100" t="s">
         <v>15</v>
@@ -6641,7 +6655,7 @@
         <v>15</v>
       </c>
       <c r="K100" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L100" t="s">
         <v>127</v>
@@ -6649,7 +6663,7 @@
     </row>
     <row r="101" ht="40.5" spans="1:12">
       <c r="A101" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B101" t="s">
         <v>22</v>
@@ -6667,7 +6681,7 @@
         <v>15</v>
       </c>
       <c r="G101" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="H101" t="s">
         <v>15</v>
@@ -6682,12 +6696,12 @@
         <v>147</v>
       </c>
       <c r="L101" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="102" ht="30" spans="1:12">
       <c r="A102" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B102" t="s">
         <v>22</v>
@@ -6705,7 +6719,7 @@
         <v>15</v>
       </c>
       <c r="G102" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H102" t="s">
         <v>15</v>
@@ -6717,12 +6731,12 @@
         <v>15</v>
       </c>
       <c r="L102" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="103" ht="40.5" spans="1:12">
       <c r="A103" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B103" t="s">
         <v>13</v>
@@ -6740,7 +6754,7 @@
         <v>15</v>
       </c>
       <c r="G103" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H103" t="s">
         <v>15</v>
@@ -6760,7 +6774,7 @@
     </row>
     <row r="104" ht="43.5" spans="1:12">
       <c r="A104" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B104" t="s">
         <v>22</v>
@@ -6778,7 +6792,7 @@
         <v>15</v>
       </c>
       <c r="G104" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H104" t="s">
         <v>15</v>
@@ -6793,12 +6807,12 @@
         <v>15</v>
       </c>
       <c r="L104" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="105" ht="54" spans="1:12">
       <c r="A105" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B105" t="s">
         <v>22</v>
@@ -6816,7 +6830,7 @@
         <v>15</v>
       </c>
       <c r="G105" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H105" t="s">
         <v>15</v>
@@ -6831,12 +6845,12 @@
         <v>15</v>
       </c>
       <c r="L105" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="106" ht="30" spans="1:12">
       <c r="A106" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B106" t="s">
         <v>22</v>
@@ -6854,7 +6868,7 @@
         <v>15</v>
       </c>
       <c r="G106" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="H106" t="s">
         <v>15</v>
@@ -6869,12 +6883,12 @@
         <v>15</v>
       </c>
       <c r="L106" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="107" ht="55.5" spans="1:12">
       <c r="A107" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B107" t="s">
         <v>13</v>
@@ -6892,7 +6906,7 @@
         <v>15</v>
       </c>
       <c r="G107" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="H107" t="s">
         <v>15</v>
@@ -6912,7 +6926,7 @@
     </row>
     <row r="108" ht="40.5" spans="1:12">
       <c r="A108" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B108" t="s">
         <v>13</v>
@@ -6930,7 +6944,7 @@
         <v>15</v>
       </c>
       <c r="G108" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="H108" t="s">
         <v>15</v>
@@ -6942,10 +6956,10 @@
         <v>15</v>
       </c>
       <c r="K108" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L108" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -6966,47 +6980,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B5" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
@@ -7014,7 +7028,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -7022,66 +7036,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B10" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B11" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B13" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B14" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -7103,616 +7117,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="D3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B5" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C5" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D5" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E5" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F5" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C6" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B7" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D7" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F7" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E8" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F8" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B10" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C10" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D10" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E10" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F10" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B11" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C11" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="D11" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E11" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="F11" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B12" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C12" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D12" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E12" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F12" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B13" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C13" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D13" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E13" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F13" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B15" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C15" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D15" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E15" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F15" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B16" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C16" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D16" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E16" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F16" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B17" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C17" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D17" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E17" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F17" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B18" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="C18" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D18" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E18" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="F18" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B19" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C19" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D19" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E19" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="F19" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B20" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C20" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D20" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E20" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="F20" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B21" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C21" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D21" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E21" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F21" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B22" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C22" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D22" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E22" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F22" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B23" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C23" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D23" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E23" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F23" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B24" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C24" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D24" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E24" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F24" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B25" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C25" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D25" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E25" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F25" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B26" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C26" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D26" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E26" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="F26" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B27" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C27" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D27" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E27" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F27" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B28" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C28" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D28" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E28" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F28" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B29" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C29" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D29" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E29" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="F29" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="B30" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C30" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D30" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E30" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F30" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B31" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C31" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D31" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>
